--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118808050</v>
+        <v>118807190</v>
       </c>
       <c r="B2" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503917</v>
+        <v>503885</v>
       </c>
       <c r="R2" t="n">
-        <v>6818291</v>
+        <v>6818113</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118807599</v>
+        <v>118809168</v>
       </c>
       <c r="B3" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503936</v>
+        <v>503993</v>
       </c>
       <c r="R3" t="n">
-        <v>6818044</v>
+        <v>6818483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118808488</v>
+        <v>118807878</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503919</v>
+        <v>503935</v>
       </c>
       <c r="R4" t="n">
-        <v>6818388</v>
+        <v>6818149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118808450</v>
+        <v>118808488</v>
       </c>
       <c r="B5" t="n">
-        <v>8416</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503971</v>
+        <v>503919</v>
       </c>
       <c r="R5" t="n">
-        <v>6818421</v>
+        <v>6818388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809168</v>
+        <v>118807983</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1179,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503993</v>
+        <v>503944</v>
       </c>
       <c r="R6" t="n">
-        <v>6818483</v>
+        <v>6818237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118809141</v>
+        <v>118807341</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503988</v>
+        <v>503911</v>
       </c>
       <c r="R7" t="n">
-        <v>6818468</v>
+        <v>6818087</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118807923</v>
+        <v>118807599</v>
       </c>
       <c r="B8" t="n">
-        <v>78220</v>
+        <v>8416</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1359,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503925</v>
+        <v>503936</v>
       </c>
       <c r="R8" t="n">
-        <v>6818175</v>
+        <v>6818044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,6 +1450,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1479,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118808385</v>
+        <v>118808959</v>
       </c>
       <c r="B9" t="n">
-        <v>79525</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503907</v>
+        <v>503980</v>
       </c>
       <c r="R9" t="n">
-        <v>6818341</v>
+        <v>6818425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118807983</v>
+        <v>118808483</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503944</v>
+        <v>503914</v>
       </c>
       <c r="R10" t="n">
-        <v>6818237</v>
+        <v>6818389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118807474</v>
+        <v>118807049</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1743,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503933</v>
+        <v>503865</v>
       </c>
       <c r="R11" t="n">
-        <v>6818083</v>
+        <v>6818135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118807334</v>
+        <v>118808450</v>
       </c>
       <c r="B12" t="n">
-        <v>78220</v>
+        <v>8416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,38 +1817,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503911</v>
+        <v>503971</v>
       </c>
       <c r="R12" t="n">
-        <v>6818087</v>
+        <v>6818421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118807864</v>
+        <v>118808385</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>79525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,38 +1939,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503935</v>
+        <v>503907</v>
       </c>
       <c r="R13" t="n">
-        <v>6818149</v>
+        <v>6818341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118808319</v>
+        <v>118808032</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2055,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503929</v>
+        <v>503904</v>
       </c>
       <c r="R14" t="n">
-        <v>6818344</v>
+        <v>6818257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118807715</v>
+        <v>118808050</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,37 +2167,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503991</v>
+        <v>503917</v>
       </c>
       <c r="R15" t="n">
-        <v>6818090</v>
+        <v>6818291</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118808548</v>
+        <v>118807547</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503944</v>
+        <v>503925</v>
       </c>
       <c r="R16" t="n">
-        <v>6818382</v>
+        <v>6818054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118807190</v>
+        <v>118807923</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2391,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503885</v>
+        <v>503925</v>
       </c>
       <c r="R17" t="n">
-        <v>6818113</v>
+        <v>6818175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118807547</v>
+        <v>118809258</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,38 +2499,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503925</v>
+        <v>503993</v>
       </c>
       <c r="R18" t="n">
-        <v>6818054</v>
+        <v>6818483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118808959</v>
+        <v>118808319</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503980</v>
+        <v>503929</v>
       </c>
       <c r="R19" t="n">
-        <v>6818425</v>
+        <v>6818344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118808032</v>
+        <v>118809141</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,34 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503904</v>
+        <v>503988</v>
       </c>
       <c r="R20" t="n">
-        <v>6818257</v>
+        <v>6818468</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,7 +2828,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118807341</v>
+        <v>118809159</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2859,14 +2864,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503911</v>
+        <v>503982</v>
       </c>
       <c r="R21" t="n">
-        <v>6818087</v>
+        <v>6818475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118808283</v>
+        <v>118807474</v>
       </c>
       <c r="B22" t="n">
-        <v>79525</v>
+        <v>78484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,38 +2952,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503925</v>
+        <v>503933</v>
       </c>
       <c r="R22" t="n">
-        <v>6818356</v>
+        <v>6818083</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3010,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118808483</v>
+        <v>118807715</v>
       </c>
       <c r="B23" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,34 +3068,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503914</v>
+        <v>503991</v>
       </c>
       <c r="R23" t="n">
-        <v>6818389</v>
+        <v>6818090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118807049</v>
+        <v>118807334</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503911</v>
       </c>
       <c r="R24" t="n">
-        <v>6818135</v>
+        <v>6818087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118809258</v>
+        <v>118808548</v>
       </c>
       <c r="B25" t="n">
-        <v>8416</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,43 +3288,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503993</v>
+        <v>503944</v>
       </c>
       <c r="R25" t="n">
-        <v>6818483</v>
+        <v>6818382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809159</v>
+        <v>118808283</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>79525</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,25 +3400,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503982</v>
+        <v>503925</v>
       </c>
       <c r="R26" t="n">
-        <v>6818475</v>
+        <v>6818356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118807190</v>
+        <v>118808488</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503885</v>
+        <v>503919</v>
       </c>
       <c r="R2" t="n">
-        <v>6818113</v>
+        <v>6818388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118809168</v>
+        <v>118807190</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503993</v>
+        <v>503885</v>
       </c>
       <c r="R3" t="n">
-        <v>6818483</v>
+        <v>6818113</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118807878</v>
+        <v>118809168</v>
       </c>
       <c r="B4" t="n">
         <v>78484</v>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503935</v>
+        <v>503993</v>
       </c>
       <c r="R4" t="n">
-        <v>6818149</v>
+        <v>6818483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118808488</v>
+        <v>118807878</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503919</v>
+        <v>503935</v>
       </c>
       <c r="R5" t="n">
-        <v>6818388</v>
+        <v>6818149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118808488</v>
+        <v>118808050</v>
       </c>
       <c r="B2" t="n">
         <v>78221</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503919</v>
+        <v>503917</v>
       </c>
       <c r="R2" t="n">
-        <v>6818388</v>
+        <v>6818291</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118807190</v>
+        <v>118808319</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503885</v>
+        <v>503929</v>
       </c>
       <c r="R3" t="n">
-        <v>6818113</v>
+        <v>6818344</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118809168</v>
+        <v>118808450</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503993</v>
+        <v>503971</v>
       </c>
       <c r="R4" t="n">
-        <v>6818483</v>
+        <v>6818421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1002,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118807878</v>
+        <v>118807341</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503935</v>
+        <v>503911</v>
       </c>
       <c r="R5" t="n">
-        <v>6818149</v>
+        <v>6818087</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118807983</v>
+        <v>118807599</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503944</v>
+        <v>503936</v>
       </c>
       <c r="R6" t="n">
-        <v>6818237</v>
+        <v>6818044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118807341</v>
+        <v>118808032</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1275,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503911</v>
+        <v>503904</v>
       </c>
       <c r="R7" t="n">
-        <v>6818087</v>
+        <v>6818257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118807599</v>
+        <v>118808548</v>
       </c>
       <c r="B8" t="n">
-        <v>8416</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,47 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503936</v>
+        <v>503944</v>
       </c>
       <c r="R8" t="n">
-        <v>6818044</v>
+        <v>6818382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1461,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118808959</v>
+        <v>118807474</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1505,14 +1515,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503980</v>
+        <v>503933</v>
       </c>
       <c r="R9" t="n">
-        <v>6818425</v>
+        <v>6818083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118808483</v>
+        <v>118808283</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
+        <v>79525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503914</v>
+        <v>503925</v>
       </c>
       <c r="R10" t="n">
-        <v>6818389</v>
+        <v>6818356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118807049</v>
+        <v>118807923</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503865</v>
+        <v>503925</v>
       </c>
       <c r="R11" t="n">
-        <v>6818135</v>
+        <v>6818175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118808450</v>
+        <v>118809159</v>
       </c>
       <c r="B12" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,47 +1827,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503971</v>
+        <v>503982</v>
       </c>
       <c r="R12" t="n">
-        <v>6818421</v>
+        <v>6818475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118808385</v>
+        <v>118807864</v>
       </c>
       <c r="B13" t="n">
-        <v>79525</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,38 +1939,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503907</v>
+        <v>503935</v>
       </c>
       <c r="R13" t="n">
-        <v>6818341</v>
+        <v>6818149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118808032</v>
+        <v>118808483</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2055,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503904</v>
+        <v>503914</v>
       </c>
       <c r="R14" t="n">
-        <v>6818257</v>
+        <v>6818389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118808050</v>
+        <v>118807168</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,37 +2167,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503917</v>
+        <v>503885</v>
       </c>
       <c r="R15" t="n">
-        <v>6818291</v>
+        <v>6818113</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118807547</v>
+        <v>118809141</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503925</v>
+        <v>503988</v>
       </c>
       <c r="R16" t="n">
-        <v>6818054</v>
+        <v>6818468</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118807923</v>
+        <v>118809168</v>
       </c>
       <c r="B17" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,34 +2391,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503925</v>
+        <v>503993</v>
       </c>
       <c r="R17" t="n">
-        <v>6818175</v>
+        <v>6818483</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118808319</v>
+        <v>118808385</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>79525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,25 +2616,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503929</v>
+        <v>503907</v>
       </c>
       <c r="R19" t="n">
-        <v>6818344</v>
+        <v>6818341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118809141</v>
+        <v>118808488</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>78221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503988</v>
+        <v>503919</v>
       </c>
       <c r="R20" t="n">
-        <v>6818468</v>
+        <v>6818388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118809159</v>
+        <v>118808959</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503982</v>
+        <v>503980</v>
       </c>
       <c r="R21" t="n">
-        <v>6818475</v>
+        <v>6818425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118807474</v>
+        <v>118807334</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503933</v>
+        <v>503911</v>
       </c>
       <c r="R22" t="n">
-        <v>6818083</v>
+        <v>6818087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118807715</v>
+        <v>118807547</v>
       </c>
       <c r="B23" t="n">
         <v>78484</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503991</v>
+        <v>503925</v>
       </c>
       <c r="R23" t="n">
-        <v>6818090</v>
+        <v>6818054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118807334</v>
+        <v>118807049</v>
       </c>
       <c r="B24" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503911</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
-        <v>6818087</v>
+        <v>6818135</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118808548</v>
+        <v>118807715</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,34 +3292,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503944</v>
+        <v>503991</v>
       </c>
       <c r="R25" t="n">
-        <v>6818382</v>
+        <v>6818090</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118808283</v>
+        <v>118807983</v>
       </c>
       <c r="B26" t="n">
-        <v>79525</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,38 +3400,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503925</v>
+        <v>503944</v>
       </c>
       <c r="R26" t="n">
-        <v>6818356</v>
+        <v>6818237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118808050</v>
+        <v>118807168</v>
       </c>
       <c r="B2" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503917</v>
+        <v>503885</v>
       </c>
       <c r="R2" t="n">
-        <v>6818291</v>
+        <v>6818113</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118808319</v>
+        <v>118808032</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503929</v>
+        <v>503904</v>
       </c>
       <c r="R3" t="n">
-        <v>6818344</v>
+        <v>6818257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118808450</v>
+        <v>118807864</v>
       </c>
       <c r="B4" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503971</v>
+        <v>503935</v>
       </c>
       <c r="R4" t="n">
-        <v>6818421</v>
+        <v>6818149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118807341</v>
+        <v>118809159</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503911</v>
+        <v>503982</v>
       </c>
       <c r="R5" t="n">
-        <v>6818087</v>
+        <v>6818475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118807599</v>
+        <v>118809141</v>
       </c>
       <c r="B6" t="n">
-        <v>8416</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,47 +1135,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503936</v>
+        <v>503988</v>
       </c>
       <c r="R6" t="n">
-        <v>6818044</v>
+        <v>6818468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118808032</v>
+        <v>118808050</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,37 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503904</v>
+        <v>503917</v>
       </c>
       <c r="R7" t="n">
-        <v>6818257</v>
+        <v>6818291</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118808548</v>
+        <v>118808283</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503944</v>
+        <v>503925</v>
       </c>
       <c r="R8" t="n">
-        <v>6818382</v>
+        <v>6818356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1462,7 @@
         <v>118807474</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1591,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118808283</v>
+        <v>118807715</v>
       </c>
       <c r="B10" t="n">
-        <v>79525</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,38 +1583,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503925</v>
+        <v>503991</v>
       </c>
       <c r="R10" t="n">
-        <v>6818356</v>
+        <v>6818090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118807923</v>
+        <v>118809168</v>
       </c>
       <c r="B11" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503925</v>
+        <v>503993</v>
       </c>
       <c r="R11" t="n">
-        <v>6818175</v>
+        <v>6818483</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809159</v>
+        <v>118807923</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503982</v>
+        <v>503925</v>
       </c>
       <c r="R12" t="n">
-        <v>6818475</v>
+        <v>6818175</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118807864</v>
+        <v>118808488</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,34 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503935</v>
+        <v>503919</v>
       </c>
       <c r="R13" t="n">
-        <v>6818149</v>
+        <v>6818388</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118808483</v>
+        <v>118807599</v>
       </c>
       <c r="B14" t="n">
-        <v>78220</v>
+        <v>8416</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,38 +2031,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503914</v>
+        <v>503936</v>
       </c>
       <c r="R14" t="n">
-        <v>6818389</v>
+        <v>6818044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2122,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118807168</v>
+        <v>118809258</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,38 +2153,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503885</v>
+        <v>503993</v>
       </c>
       <c r="R15" t="n">
-        <v>6818113</v>
+        <v>6818483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118809141</v>
+        <v>118807547</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,34 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503988</v>
+        <v>503925</v>
       </c>
       <c r="R16" t="n">
-        <v>6818468</v>
+        <v>6818054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118809168</v>
+        <v>118808959</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503993</v>
+        <v>503980</v>
       </c>
       <c r="R17" t="n">
-        <v>6818483</v>
+        <v>6818425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118809258</v>
+        <v>118807983</v>
       </c>
       <c r="B18" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,43 +2494,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503993</v>
+        <v>503944</v>
       </c>
       <c r="R18" t="n">
-        <v>6818483</v>
+        <v>6818237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118808385</v>
+        <v>118807049</v>
       </c>
       <c r="B19" t="n">
-        <v>79525</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,38 +2606,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503907</v>
+        <v>503865</v>
       </c>
       <c r="R19" t="n">
-        <v>6818341</v>
+        <v>6818135</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118808488</v>
+        <v>118808385</v>
       </c>
       <c r="B20" t="n">
-        <v>78221</v>
+        <v>79532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503919</v>
+        <v>503907</v>
       </c>
       <c r="R20" t="n">
-        <v>6818388</v>
+        <v>6818341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118808959</v>
+        <v>118808483</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503980</v>
+        <v>503914</v>
       </c>
       <c r="R21" t="n">
-        <v>6818425</v>
+        <v>6818389</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118807334</v>
+        <v>118808548</v>
       </c>
       <c r="B22" t="n">
-        <v>78220</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,34 +2946,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503911</v>
+        <v>503944</v>
       </c>
       <c r="R22" t="n">
-        <v>6818087</v>
+        <v>6818382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118807547</v>
+        <v>118807334</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,21 +3058,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3092,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503925</v>
+        <v>503911</v>
       </c>
       <c r="R23" t="n">
-        <v>6818054</v>
+        <v>6818087</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118807049</v>
+        <v>118808450</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,38 +3166,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503971</v>
       </c>
       <c r="R24" t="n">
-        <v>6818135</v>
+        <v>6818421</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,6 +3257,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118807715</v>
+        <v>118807341</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503991</v>
+        <v>503911</v>
       </c>
       <c r="R25" t="n">
-        <v>6818090</v>
+        <v>6818087</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118807983</v>
+        <v>118808319</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,34 +3404,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503944</v>
+        <v>503929</v>
       </c>
       <c r="R26" t="n">
-        <v>6818237</v>
+        <v>6818344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118807715</v>
+        <v>118807923</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503991</v>
+        <v>503925</v>
       </c>
       <c r="R10" t="n">
-        <v>6818090</v>
+        <v>6818175</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809168</v>
+        <v>118807715</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1719,14 +1719,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503993</v>
+        <v>503991</v>
       </c>
       <c r="R11" t="n">
-        <v>6818483</v>
+        <v>6818090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118807923</v>
+        <v>118809168</v>
       </c>
       <c r="B12" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503925</v>
+        <v>503993</v>
       </c>
       <c r="R12" t="n">
-        <v>6818175</v>
+        <v>6818483</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118807599</v>
+        <v>118809258</v>
       </c>
       <c r="B14" t="n">
         <v>8416</v>
@@ -2053,25 +2053,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503936</v>
+        <v>503993</v>
       </c>
       <c r="R14" t="n">
-        <v>6818044</v>
+        <v>6818483</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,7 +2118,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2141,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809258</v>
+        <v>118807599</v>
       </c>
       <c r="B15" t="n">
         <v>8416</v>
@@ -2175,21 +2170,25 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503993</v>
+        <v>503936</v>
       </c>
       <c r="R15" t="n">
-        <v>6818483</v>
+        <v>6818044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,6 +2239,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28217-2024 artfynd.xlsx
+++ b/artfynd/A 28217-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118807168</v>
+        <v>118809168</v>
       </c>
       <c r="B2" t="n">
         <v>78491</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503885</v>
+        <v>503993</v>
       </c>
       <c r="R2" t="n">
-        <v>6818113</v>
+        <v>6818483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118808032</v>
+        <v>118807190</v>
       </c>
       <c r="B3" t="n">
         <v>78491</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503904</v>
+        <v>503885</v>
       </c>
       <c r="R3" t="n">
-        <v>6818257</v>
+        <v>6818113</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118807864</v>
+        <v>118808319</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503935</v>
+        <v>503929</v>
       </c>
       <c r="R4" t="n">
-        <v>6818149</v>
+        <v>6818344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118809159</v>
+        <v>118808050</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503982</v>
+        <v>503917</v>
       </c>
       <c r="R5" t="n">
-        <v>6818475</v>
+        <v>6818291</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809141</v>
+        <v>118807334</v>
       </c>
       <c r="B6" t="n">
-        <v>79572</v>
+        <v>78227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503988</v>
+        <v>503911</v>
       </c>
       <c r="R6" t="n">
-        <v>6818468</v>
+        <v>6818087</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118808050</v>
+        <v>118808283</v>
       </c>
       <c r="B7" t="n">
-        <v>78228</v>
+        <v>79532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503917</v>
+        <v>503925</v>
       </c>
       <c r="R7" t="n">
-        <v>6818291</v>
+        <v>6818356</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118808283</v>
+        <v>118808385</v>
       </c>
       <c r="B8" t="n">
         <v>79532</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503925</v>
+        <v>503907</v>
       </c>
       <c r="R8" t="n">
-        <v>6818356</v>
+        <v>6818341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118807474</v>
+        <v>118807878</v>
       </c>
       <c r="B9" t="n">
         <v>78491</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503933</v>
+        <v>503935</v>
       </c>
       <c r="R9" t="n">
-        <v>6818083</v>
+        <v>6818149</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118807923</v>
+        <v>118808483</v>
       </c>
       <c r="B10" t="n">
         <v>78227</v>
@@ -1607,14 +1607,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503925</v>
+        <v>503914</v>
       </c>
       <c r="R10" t="n">
-        <v>6818175</v>
+        <v>6818389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118807715</v>
+        <v>118807983</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503991</v>
+        <v>503944</v>
       </c>
       <c r="R11" t="n">
-        <v>6818090</v>
+        <v>6818237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809168</v>
+        <v>118809258</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>8416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,28 +1807,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstenssnåret (Storstenssnåret), Dlr</t>
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118808488</v>
+        <v>118808548</v>
       </c>
       <c r="B13" t="n">
-        <v>78228</v>
+        <v>79572</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503919</v>
+        <v>503944</v>
       </c>
       <c r="R13" t="n">
-        <v>6818388</v>
+        <v>6818382</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809258</v>
+        <v>118807715</v>
       </c>
       <c r="B14" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,43 +2036,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503993</v>
+        <v>503991</v>
       </c>
       <c r="R14" t="n">
-        <v>6818483</v>
+        <v>6818090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118807599</v>
+        <v>118807049</v>
       </c>
       <c r="B15" t="n">
-        <v>8416</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,47 +2148,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503936</v>
+        <v>503865</v>
       </c>
       <c r="R15" t="n">
-        <v>6818044</v>
+        <v>6818135</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,7 +2230,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2258,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118807547</v>
+        <v>118808032</v>
       </c>
       <c r="B16" t="n">
         <v>78491</v>
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503925</v>
+        <v>503904</v>
       </c>
       <c r="R16" t="n">
-        <v>6818054</v>
+        <v>6818257</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2360,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118808959</v>
+        <v>118807547</v>
       </c>
       <c r="B17" t="n">
         <v>78491</v>
@@ -2406,14 +2396,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503980</v>
+        <v>503925</v>
       </c>
       <c r="R17" t="n">
-        <v>6818425</v>
+        <v>6818054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118807983</v>
+        <v>118807923</v>
       </c>
       <c r="B18" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2522,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503944</v>
+        <v>503925</v>
       </c>
       <c r="R18" t="n">
-        <v>6818237</v>
+        <v>6818175</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2557,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,7 +2584,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118807049</v>
+        <v>118809159</v>
       </c>
       <c r="B19" t="n">
         <v>78491</v>
@@ -2630,14 +2620,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503865</v>
+        <v>503982</v>
       </c>
       <c r="R19" t="n">
-        <v>6818135</v>
+        <v>6818475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2669,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118808385</v>
+        <v>118808959</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,25 +2708,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503907</v>
+        <v>503980</v>
       </c>
       <c r="R20" t="n">
-        <v>6818341</v>
+        <v>6818425</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118808483</v>
+        <v>118808488</v>
       </c>
       <c r="B21" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,21 +2824,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503914</v>
+        <v>503919</v>
       </c>
       <c r="R21" t="n">
-        <v>6818389</v>
+        <v>6818388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118808548</v>
+        <v>118807474</v>
       </c>
       <c r="B22" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,34 +2936,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503944</v>
+        <v>503933</v>
       </c>
       <c r="R22" t="n">
-        <v>6818382</v>
+        <v>6818083</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118807334</v>
+        <v>118807599</v>
       </c>
       <c r="B23" t="n">
-        <v>78227</v>
+        <v>8416</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,38 +3044,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503911</v>
+        <v>503936</v>
       </c>
       <c r="R23" t="n">
-        <v>6818087</v>
+        <v>6818044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,6 +3135,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118807341</v>
+        <v>118809141</v>
       </c>
       <c r="B25" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,34 +3292,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
+          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503911</v>
+        <v>503988</v>
       </c>
       <c r="R25" t="n">
-        <v>6818087</v>
+        <v>6818468</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118808319</v>
+        <v>118807341</v>
       </c>
       <c r="B26" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,34 +3404,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storstenssnåret (Storstenssnåret), Dlr</t>
+          <t>Stallsmyrkojan (Stallsmyrkojan), Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503929</v>
+        <v>503911</v>
       </c>
       <c r="R26" t="n">
-        <v>6818344</v>
+        <v>6818087</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
